--- a/output/pdf_financials_xlsx/QIM.xlsx
+++ b/output/pdf_financials_xlsx/QIM.xlsx
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.300588</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.714412</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.682393</v>
       </c>
     </row>
     <row r="93">
@@ -3185,7 +3185,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4242,7 +4246,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>0.300588</v>
       </c>

--- a/output/pdf_financials_xlsx/QIM.xlsx
+++ b/output/pdf_financials_xlsx/QIM.xlsx
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.013089</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000488</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.212785</v>
+        <v>-1.225874</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.982954</v>
+        <v>-2.983442</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.212785</v>
+        <v>-1.225874</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.982954</v>
+        <v>-2.983442</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1024,13 +1024,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.020656</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.047354</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>12.443437</v>
       </c>
     </row>
     <row r="35">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.020656</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.047354</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>12.443437</v>
       </c>
     </row>
     <row r="37">
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.084394</v>
+        <v>0.063738</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.247123</v>
+        <v>0.199769</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>13.014572</v>
+        <v>0.5711349999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">

--- a/output/pdf_financials_xlsx/QIM.xlsx
+++ b/output/pdf_financials_xlsx/QIM.xlsx
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.65219</v>
+        <v>0.6621899999999999</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>1.177836</v>
@@ -4742,7 +4742,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -6414,7 +6418,11 @@
           <t>Shares issued for cash (Note 7)</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E121" s="5" t="n">
         <v>1.017802</v>
       </c>
@@ -7497,7 +7505,11 @@
           <t>Directors’ fees (Note 9)</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
         <v>0.01</v>
       </c>
